--- a/demo/intesa_lista_operazioni_13m.xlsx
+++ b/demo/intesa_lista_operazioni_13m.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,138 +441,78 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Conti e Carte:</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Conto 1000 / 00012345</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Finanziamento:</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Operazione</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Dettagli</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Importo</t>
         </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bonifico disposto</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Rossi Immobiliare canone locazione</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Casa</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>-850</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45812</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Bonifico disposto</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>T.R. Bank Gmbh Berlino</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Trasferimenti</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>-400</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>45813</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pagamento POS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ricarica carta Dublino</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Trasferimenti</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>-300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45815</v>
+        <v>45809</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -581,26 +521,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>-150</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45816</v>
+        <v>45812</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -609,12 +549,12 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-20.77</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45817</v>
+        <v>45813</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -623,12 +563,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -637,26 +577,26 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-64.02</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45820</v>
+        <v>45815</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -665,12 +605,12 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-80.48</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45820</v>
+        <v>45816</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -679,12 +619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -693,26 +633,26 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-49.67</v>
+        <v>-20.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45824</v>
+        <v>45817</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -721,26 +661,26 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>-29.9</v>
+        <v>-64.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45827</v>
+        <v>45820</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -749,12 +689,12 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>-26.61</v>
+        <v>-80.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45830</v>
+        <v>45820</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -763,12 +703,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -777,26 +717,26 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>-29.4</v>
+        <v>-49.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45834</v>
+        <v>45824</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -805,26 +745,26 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>-60.48</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45835</v>
+        <v>45827</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -833,26 +773,26 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2480.84</v>
+        <v>-26.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45839</v>
+        <v>45830</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -861,12 +801,12 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>-850</v>
+        <v>-29.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45840</v>
+        <v>45834</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -875,7 +815,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -889,26 +829,26 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>-85.53</v>
+        <v>-60.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45841</v>
+        <v>45835</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -917,12 +857,12 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>-63.94</v>
+        <v>2480.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45842</v>
+        <v>45839</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -931,12 +871,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -945,12 +885,12 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>-400</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45842</v>
+        <v>45840</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -959,12 +899,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eni Station Milano Est</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -973,12 +913,12 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>-60.68</v>
+        <v>-85.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45843</v>
+        <v>45841</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -987,12 +927,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1001,21 +941,21 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>-68.14</v>
+        <v>-63.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45843</v>
+        <v>45842</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1029,12 +969,12 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>-300</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45844</v>
+        <v>45842</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1043,12 +983,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Eni Station Milano Est</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1057,12 +997,12 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>-87.26000000000001</v>
+        <v>-60.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45847</v>
+        <v>45843</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1071,12 +1011,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1085,26 +1025,26 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>-92.12</v>
+        <v>-68.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45854</v>
+        <v>45843</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1113,12 +1053,12 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>-29.9</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45854</v>
+        <v>45844</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1127,12 +1067,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1141,26 +1081,26 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>-48.72</v>
+        <v>-87.26000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45854</v>
+        <v>45847</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1169,26 +1109,26 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>-200</v>
+        <v>-92.12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45863</v>
+        <v>45854</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1197,26 +1137,26 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>-51.6</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45865</v>
+        <v>45854</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Ristorante Da Gino Milano</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1225,26 +1165,26 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2465.99</v>
+        <v>-48.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45870</v>
+        <v>45854</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1253,26 +1193,26 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>-850</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45873</v>
+        <v>45863</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1281,26 +1221,26 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>-400</v>
+        <v>-51.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45874</v>
+        <v>45865</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1309,26 +1249,26 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>-300</v>
+        <v>2465.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45878</v>
+        <v>45870</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1337,26 +1277,26 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>-56.07</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45878</v>
+        <v>45873</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1365,26 +1305,26 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>-150</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45881</v>
+        <v>45874</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1393,26 +1333,26 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>-60.89</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45885</v>
+        <v>45878</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1421,26 +1361,26 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>-29.9</v>
+        <v>-56.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45886</v>
+        <v>45878</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1449,26 +1389,26 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>-86.23</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45888</v>
+        <v>45881</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1477,26 +1417,26 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>-83.43000000000001</v>
+        <v>-60.89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45892</v>
+        <v>45885</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1505,12 +1445,12 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>-60</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45893</v>
+        <v>45886</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1519,12 +1459,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1533,26 +1473,26 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>-52.4</v>
+        <v>-86.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45896</v>
+        <v>45888</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1561,26 +1501,26 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2482.26</v>
+        <v>-83.43000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45901</v>
+        <v>45892</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1589,12 +1529,12 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>-850</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45903</v>
+        <v>45893</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1603,12 +1543,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1617,26 +1557,26 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>-82.13</v>
+        <v>-52.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45904</v>
+        <v>45896</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1645,26 +1585,26 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>-400</v>
+        <v>2482.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45905</v>
+        <v>45901</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1673,26 +1613,26 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-300</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45913</v>
+        <v>45903</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1701,26 +1641,26 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>-150</v>
+        <v>-82.13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45915</v>
+        <v>45904</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1729,12 +1669,12 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>-59.78</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45915</v>
+        <v>45905</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1743,12 +1683,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1757,26 +1697,26 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>-49.88</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45916</v>
+        <v>45913</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1785,12 +1725,12 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>-29.9</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45918</v>
+        <v>45915</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1799,12 +1739,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eni Station Milano Est</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1813,12 +1753,12 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>-38.19</v>
+        <v>-59.78</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45918</v>
+        <v>45915</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1827,12 +1767,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pizzeria Bella Napoli Milano</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1841,26 +1781,26 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>-54.6</v>
+        <v>-49.88</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45927</v>
+        <v>45916</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1869,12 +1809,12 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2478.26</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45928</v>
+        <v>45918</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1883,12 +1823,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Eni Station Milano Est</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1897,26 +1837,26 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>-90.84999999999999</v>
+        <v>-38.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45931</v>
+        <v>45918</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Pizzeria Bella Napoli Milano</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1925,26 +1865,26 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>-850</v>
+        <v>-54.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45934</v>
+        <v>45927</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1953,26 +1893,26 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-29.73</v>
+        <v>2478.26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45934</v>
+        <v>45928</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1981,26 +1921,26 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-400</v>
+        <v>-90.84999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45935</v>
+        <v>45931</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2009,12 +1949,12 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-300</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45938</v>
+        <v>45934</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2023,12 +1963,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2037,26 +1977,26 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-68.87</v>
+        <v>-29.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45942</v>
+        <v>45934</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2065,12 +2005,12 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>-56.24</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45944</v>
+        <v>45935</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2079,12 +2019,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2093,26 +2033,26 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-56.67</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45946</v>
+        <v>45938</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2121,26 +2061,26 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>-29.9</v>
+        <v>-68.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45946</v>
+        <v>45942</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2149,12 +2089,12 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>-77.05</v>
+        <v>-56.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45947</v>
+        <v>45944</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2163,12 +2103,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Ristorante Da Gino Milano</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2177,26 +2117,26 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>-61.43</v>
+        <v>-56.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45948</v>
+        <v>45946</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2205,26 +2145,26 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-150</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45957</v>
+        <v>45946</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2233,26 +2173,26 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2451.61</v>
+        <v>-77.05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45962</v>
+        <v>45947</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2261,26 +2201,26 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>-850</v>
+        <v>-61.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45965</v>
+        <v>45948</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2289,26 +2229,26 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-400</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45966</v>
+        <v>45957</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2317,26 +2257,26 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>-300</v>
+        <v>2451.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45970</v>
+        <v>45962</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2345,26 +2285,26 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>-43.54</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45971</v>
+        <v>45965</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2373,12 +2313,12 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>-39.53</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45971</v>
+        <v>45966</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2387,12 +2327,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2401,12 +2341,12 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>-61.04</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45973</v>
+        <v>45970</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2415,12 +2355,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2429,26 +2369,26 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>-55.54</v>
+        <v>-43.54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45977</v>
+        <v>45971</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2457,26 +2397,26 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>-29.9</v>
+        <v>-39.53</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45981</v>
+        <v>45971</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2485,12 +2425,12 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>-100</v>
+        <v>-61.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45983</v>
+        <v>45973</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2499,7 +2439,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2513,26 +2453,26 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>-43.9</v>
+        <v>-55.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45985</v>
+        <v>45977</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2541,26 +2481,26 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>-60.8</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45988</v>
+        <v>45981</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2569,12 +2509,12 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2459.75</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45988</v>
+        <v>45983</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2583,12 +2523,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2597,26 +2537,26 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>-51.19</v>
+        <v>-43.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45992</v>
+        <v>45985</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2625,26 +2565,26 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>-850</v>
+        <v>-60.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45995</v>
+        <v>45988</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2653,12 +2593,12 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>-400</v>
+        <v>2459.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45996</v>
+        <v>45988</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2667,12 +2607,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Ristorante Da Gino Milano</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2681,26 +2621,26 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>-62.2</v>
+        <v>-51.19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45996</v>
+        <v>45992</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2709,26 +2649,26 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>-300</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46000</v>
+        <v>45995</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2737,12 +2677,12 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>-33.21</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46001</v>
+        <v>45996</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2751,7 +2691,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2765,12 +2705,12 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>-93.02</v>
+        <v>-62.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46002</v>
+        <v>45996</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2779,12 +2719,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2793,12 +2733,12 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>-26.78</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46002</v>
+        <v>46000</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2807,12 +2747,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Ristorante Da Gino Milano</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2821,26 +2761,26 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>-67.12</v>
+        <v>-33.21</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2849,12 +2789,12 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>-55.57</v>
+        <v>-93.02</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46004</v>
+        <v>46002</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2863,12 +2803,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Farmacia Centrale Milano</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Salute</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2877,26 +2817,26 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>-11.64</v>
+        <v>-26.78</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46004</v>
+        <v>46002</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2905,26 +2845,26 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>-100</v>
+        <v>-67.12</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2933,26 +2873,26 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>-59.29</v>
+        <v>-55.57</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46007</v>
+        <v>46004</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Farmacia Centrale Milano</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Salute</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -2961,26 +2901,26 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>-29.9</v>
+        <v>-11.64</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46009</v>
+        <v>46004</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2989,12 +2929,12 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>-44.23</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3003,12 +2943,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eni Station Milano Est</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3017,26 +2957,26 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>-40.37</v>
+        <v>-59.29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46018</v>
+        <v>46007</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3045,26 +2985,26 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2457.18</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46023</v>
+        <v>46009</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3073,26 +3013,26 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>-850</v>
+        <v>-44.23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46026</v>
+        <v>46009</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Eni Station Milano Est</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3101,26 +3041,26 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>-400</v>
+        <v>-40.37</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46027</v>
+        <v>46018</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Eni Station Milano Est</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3129,26 +3069,26 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-57.14</v>
+        <v>2457.18</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3157,26 +3097,26 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>-300</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3185,12 +3125,12 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>-71.03</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -3199,12 +3139,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Eni Station Milano Est</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3213,26 +3153,26 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>-22.59</v>
+        <v>-57.14</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46036</v>
+        <v>46027</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3241,26 +3181,26 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>-100</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46038</v>
+        <v>46028</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3269,12 +3209,12 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>-29.9</v>
+        <v>-71.03</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46041</v>
+        <v>46028</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3283,7 +3223,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3297,26 +3237,26 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>-67.87</v>
+        <v>-22.59</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46041</v>
+        <v>46036</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eni Station Milano Est</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3325,26 +3265,26 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>-55.28</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3353,12 +3293,12 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>-88.93000000000001</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3367,12 +3307,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3381,26 +3321,26 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>-77.2</v>
+        <v>-67.87</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46049</v>
+        <v>46041</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Eni Station Milano Est</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3409,26 +3349,26 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2487.35</v>
+        <v>-55.28</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46054</v>
+        <v>46045</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3437,26 +3377,26 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>-850</v>
+        <v>-88.93000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46057</v>
+        <v>46045</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3465,26 +3405,26 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>-400</v>
+        <v>-77.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46058</v>
+        <v>46049</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3493,26 +3433,26 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>-300</v>
+        <v>2487.35</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46059</v>
+        <v>46054</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3521,26 +3461,26 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>-52.77</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46061</v>
+        <v>46057</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3549,26 +3489,26 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>-60.29</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46065</v>
+        <v>46058</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -3577,12 +3517,12 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>-62.5</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46065</v>
+        <v>46059</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -3591,12 +3531,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Farmacia Centrale Milano</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Salute</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3605,26 +3545,26 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>-21.88</v>
+        <v>-52.77</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46069</v>
+        <v>46061</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -3633,26 +3573,26 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>-29.9</v>
+        <v>-60.29</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46070</v>
+        <v>46065</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3661,12 +3601,12 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>-27.35</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46072</v>
+        <v>46065</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3675,12 +3615,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Farmacia Centrale Milano</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Salute</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3689,26 +3629,26 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>-23.28</v>
+        <v>-21.88</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46073</v>
+        <v>46069</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3717,12 +3657,12 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>-51.06</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46073</v>
+        <v>46070</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3731,12 +3671,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3745,12 +3685,12 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>-76.3</v>
+        <v>-27.35</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46074</v>
+        <v>46072</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3759,12 +3699,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3773,26 +3713,26 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>-72.65000000000001</v>
+        <v>-23.28</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46074</v>
+        <v>46073</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3801,12 +3741,12 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>-150</v>
+        <v>-51.06</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3815,12 +3755,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Ristorante Da Gino Milano</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3829,26 +3769,26 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>-66.16</v>
+        <v>-76.3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46080</v>
+        <v>46074</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3857,26 +3797,26 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>2466.53</v>
+        <v>-72.65000000000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46082</v>
+        <v>46074</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3885,26 +3825,26 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>-850</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3913,26 +3853,26 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>-400</v>
+        <v>-66.16</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46086</v>
+        <v>46080</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3941,26 +3881,26 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>-300</v>
+        <v>2466.53</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46088</v>
+        <v>46082</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3969,26 +3909,26 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>-88.09999999999999</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -3997,26 +3937,26 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>-29.9</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46097</v>
+        <v>46086</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4025,12 +3965,12 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46088</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -4039,12 +3979,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4053,26 +3993,26 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>-63.01</v>
+        <v>-88.09999999999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46097</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4081,26 +4021,26 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>-84.97</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46102</v>
+        <v>46097</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Farmacia Centrale Milano</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Salute</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4109,12 +4049,12 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>-20.78</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -4123,12 +4063,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4137,12 +4077,12 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>-49.57</v>
+        <v>-63.01</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46101</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -4151,12 +4091,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Pizzeria Bella Napoli Milano</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4165,12 +4105,12 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>-29.42</v>
+        <v>-84.97</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46102</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -4179,12 +4119,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Farmacia Centrale Milano</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Salute</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4193,26 +4133,26 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>-50.06</v>
+        <v>-20.78</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4221,26 +4161,26 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>2488.59</v>
+        <v>-49.57</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Pizzeria Bella Napoli Milano</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4249,26 +4189,26 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>-850</v>
+        <v>-29.42</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46116</v>
+        <v>46107</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4277,26 +4217,26 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>-400</v>
+        <v>-50.06</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46117</v>
+        <v>46108</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4305,26 +4245,26 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>-47.37</v>
+        <v>2488.59</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46117</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4333,26 +4273,26 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>-300</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46121</v>
+        <v>46116</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4361,12 +4301,12 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>-59.35</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46123</v>
+        <v>46117</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -4389,12 +4329,12 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>-94.95</v>
+        <v>-47.37</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46124</v>
+        <v>46117</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -4403,12 +4343,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4417,26 +4357,26 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>-71.15000000000001</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46124</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4445,26 +4385,26 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>-57.95</v>
+        <v>-59.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46128</v>
+        <v>46123</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -4473,12 +4413,12 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>-29.9</v>
+        <v>-94.95</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46132</v>
+        <v>46124</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -4487,7 +4427,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4501,26 +4441,26 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>-94.44</v>
+        <v>-71.15000000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46133</v>
+        <v>46124</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4529,26 +4469,26 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>-65.68000000000001</v>
+        <v>-57.95</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46133</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4557,12 +4497,12 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>-150</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46136</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -4571,12 +4511,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4585,26 +4525,26 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>-50.67</v>
+        <v>-94.44</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46139</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4613,26 +4553,26 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>2471.86</v>
+        <v>-65.68000000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4641,12 +4581,12 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>-850</v>
+        <v>-150</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46146</v>
+        <v>46136</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -4655,12 +4595,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4669,26 +4609,26 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>-86.09</v>
+        <v>-50.67</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4697,26 +4637,26 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-400</v>
+        <v>2471.86</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -4725,12 +4665,12 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>-19.07</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -4739,12 +4679,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -4753,26 +4693,26 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>-300</v>
+        <v>-86.09</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -4781,12 +4721,12 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>-46.38</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4795,12 +4735,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4809,12 +4749,12 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>-77.04000000000001</v>
+        <v>-19.07</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46155</v>
+        <v>46147</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4823,12 +4763,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4837,26 +4777,26 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>-69.95999999999999</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4865,26 +4805,26 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>-200</v>
+        <v>-46.38</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46158</v>
+        <v>46148</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Ristorante Da Gino Milano</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Ristoranti</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4893,12 +4833,12 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>-29.9</v>
+        <v>-77.04000000000001</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46158</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4907,12 +4847,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4921,26 +4861,26 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>-40.94</v>
+        <v>-69.95999999999999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Farmacia Centrale Milano</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Salute</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4949,26 +4889,26 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>-12.6</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46165</v>
+        <v>46158</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4977,12 +4917,12 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>-63.01</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46165</v>
+        <v>46158</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -4991,12 +4931,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Amazon Eu</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5005,12 +4945,12 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>-40.02</v>
+        <v>-40.94</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -5019,12 +4959,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Eni Station Milano Est</t>
+          <t>Farmacia Centrale Milano</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Salute</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5033,26 +4973,26 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>-47.67</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46169</v>
+        <v>46165</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Accredito stipendio</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Acme Srl emolumenti</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Stipendio</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5061,26 +5001,26 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>2488.69</v>
+        <v>-63.01</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46174</v>
+        <v>46165</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Rossi Immobiliare canone locazione</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Casa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5089,12 +5029,12 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>-850</v>
+        <v>-40.02</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -5103,12 +5043,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Carrefour Market Milano</t>
+          <t>Eni Station Milano Est</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5117,26 +5057,26 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>-75.11</v>
+        <v>-47.67</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Bonifico disposto</t>
+          <t>Accredito stipendio</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>T.R. Bank Gmbh Berlino</t>
+          <t>Acme Srl emolumenti</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Stipendio</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5145,26 +5085,26 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>-400</v>
+        <v>2488.69</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ricarica carta Dublino</t>
+          <t>Rossi Immobiliare canone locazione</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Trasferimenti</t>
+          <t>Casa</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5173,12 +5113,12 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>-300</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46179</v>
+        <v>46176</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -5187,7 +5127,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Carrefour Market Milano</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5201,26 +5141,26 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>-45.58</v>
+        <v>-75.11</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Prelievo</t>
+          <t>Bonifico disposto</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Prelievo ATM Milano</t>
+          <t>T.R. Bank Gmbh Berlino</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Contanti</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -5229,12 +5169,12 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>-200</v>
+        <v>-400</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -5243,12 +5183,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Ricarica carta Dublino</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Trasferimenti</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -5257,12 +5197,12 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>-94.04000000000001</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46183</v>
+        <v>46179</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -5271,7 +5211,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Lidl Milano Via Padova</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5285,26 +5225,26 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>-26.46</v>
+        <v>-45.58</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46185</v>
+        <v>46180</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Prelievo</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Enel Energia fornitura</t>
+          <t>Prelievo ATM Milano</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Contanti</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5313,26 +5253,26 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>-60.9</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46189</v>
+        <v>46183</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Addebito SDD</t>
+          <t>Pagamento POS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tim Spa telefono e fibra</t>
+          <t>Esselunga Milano</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Utenze</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -5341,12 +5281,12 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>-29.9</v>
+        <v>-94.04000000000001</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46191</v>
+        <v>46183</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -5355,12 +5295,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Q8 Milano V.Le Monza</t>
+          <t>Lidl Milano Via Padova</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Spesa</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -5369,26 +5309,26 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>-52.34</v>
+        <v>-26.46</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46192</v>
+        <v>46185</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ristorante Da Gino Milano</t>
+          <t>Enel Energia fornitura</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5397,26 +5337,26 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>-52.71</v>
+        <v>-60.9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46193</v>
+        <v>46189</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Pagamento POS</t>
+          <t>Addebito SDD</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Esselunga Milano</t>
+          <t>Tim Spa telefono e fibra</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Spesa</t>
+          <t>Utenze</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -5425,12 +5365,12 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>-19.22</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46196</v>
+        <v>46191</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -5439,12 +5379,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Amazon Eu</t>
+          <t>Q8 Milano V.Le Monza</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5453,34 +5393,118 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>-52.67</v>
+        <v>-52.34</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pagamento POS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ristorante Da Gino Milano</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ristoranti</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>-52.71</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pagamento POS</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Esselunga Milano</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Spesa</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>-19.22</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pagamento POS</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Amazon Eu</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>-52.67</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
         <v>46200</v>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>Accredito stipendio</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Acme Srl emolumenti</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Stipendio</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="F184" t="n">
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
         <v>2463.14</v>
       </c>
     </row>
